--- a/docs/AetherFlow_Sprint1_Updated_v3.xlsx
+++ b/docs/AetherFlow_Sprint1_Updated_v3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la\Documents\Team Project 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{403D29E2-4BFA-4D64-B21E-38BA27049ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7457F3E3-2CA6-4955-B622-55EFDB44FC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="100">
   <si>
     <t>Project</t>
   </si>
@@ -350,66 +350,6 @@
   </si>
   <si>
     <t>TBD</t>
-  </si>
-  <si>
-    <t>T201</t>
-  </si>
-  <si>
-    <t>Re-test invalid login handling after backend implementation</t>
-  </si>
-  <si>
-    <t>T202</t>
-  </si>
-  <si>
-    <t>Verify password validation enforcement</t>
-  </si>
-  <si>
-    <t>T203</t>
-  </si>
-  <si>
-    <t>Verify role-based access permissions</t>
-  </si>
-  <si>
-    <t>T204</t>
-  </si>
-  <si>
-    <t>Test duplicate SKU rejection logic</t>
-  </si>
-  <si>
-    <t>T205</t>
-  </si>
-  <si>
-    <t>Validate SKU format requirements</t>
-  </si>
-  <si>
-    <t>T206</t>
-  </si>
-  <si>
-    <t>Test inventory search functionality</t>
-  </si>
-  <si>
-    <t>T207</t>
-  </si>
-  <si>
-    <t>Verify low-stock warning alerts</t>
-  </si>
-  <si>
-    <t>T208</t>
-  </si>
-  <si>
-    <t>Document Sprint 2 QA validation results</t>
-  </si>
-  <si>
-    <t>T209</t>
-  </si>
-  <si>
-    <t>Verify Security Key masking functionality</t>
-  </si>
-  <si>
-    <t>T210</t>
-  </si>
-  <si>
-    <t>Verify mobile responsiveness on live Vercel deployment</t>
   </si>
 </sst>
 </file>
@@ -1745,6 +1685,27 @@
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1803,6 +1764,27 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2194,33 +2176,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="14"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5251,19 +5206,45 @@
       <c r="E16" s="64">
         <v>2</v>
       </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="28"/>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="F16" s="30">
+        <v>1</v>
+      </c>
+      <c r="G16" s="28">
+        <v>1</v>
+      </c>
+      <c r="H16" s="28">
+        <v>1</v>
+      </c>
+      <c r="I16" s="28">
+        <v>1</v>
+      </c>
+      <c r="J16" s="28">
+        <v>1</v>
+      </c>
+      <c r="K16" s="28">
+        <v>1</v>
+      </c>
+      <c r="L16" s="28">
+        <v>1</v>
+      </c>
+      <c r="M16" s="30">
+        <v>1</v>
+      </c>
+      <c r="N16" s="28">
+        <v>1</v>
+      </c>
+      <c r="O16" s="28">
+        <v>1</v>
+      </c>
+      <c r="P16" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="28">
+        <v>0</v>
+      </c>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
     </row>
     <row r="17" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -5343,13 +5324,27 @@
       <c r="K18" s="25">
         <v>0</v>
       </c>
-      <c r="L18" s="25"/>
-      <c r="M18" s="56"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="25"/>
+      <c r="L18" s="25">
+        <v>1</v>
+      </c>
+      <c r="M18" s="56">
+        <v>0</v>
+      </c>
+      <c r="N18" s="25">
+        <v>1</v>
+      </c>
+      <c r="O18" s="25">
+        <v>1</v>
+      </c>
+      <c r="P18" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="25">
+        <v>1</v>
+      </c>
+      <c r="R18" s="25">
+        <v>2</v>
+      </c>
       <c r="S18" s="25"/>
     </row>
     <row r="19" spans="1:19" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5386,13 +5381,27 @@
       <c r="K19" s="24">
         <v>0</v>
       </c>
-      <c r="L19" s="24"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
+      <c r="L19" s="24">
+        <v>1</v>
+      </c>
+      <c r="M19" s="30">
+        <v>0</v>
+      </c>
+      <c r="N19" s="24">
+        <v>1</v>
+      </c>
+      <c r="O19" s="24">
+        <v>1</v>
+      </c>
+      <c r="P19" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="24">
+        <v>1</v>
+      </c>
+      <c r="R19" s="24">
+        <v>2</v>
+      </c>
       <c r="S19" s="24"/>
     </row>
     <row r="20" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5429,13 +5438,27 @@
       <c r="K20" s="25">
         <v>0</v>
       </c>
-      <c r="L20" s="25"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="25"/>
+      <c r="L20" s="25">
+        <v>0</v>
+      </c>
+      <c r="M20" s="56">
+        <v>0</v>
+      </c>
+      <c r="N20" s="25">
+        <v>0</v>
+      </c>
+      <c r="O20" s="25">
+        <v>0</v>
+      </c>
+      <c r="P20" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="25">
+        <v>0</v>
+      </c>
+      <c r="R20" s="25">
+        <v>0</v>
+      </c>
       <c r="S20" s="25"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
@@ -5472,13 +5495,27 @@
       <c r="K21" s="24">
         <v>0</v>
       </c>
-      <c r="L21" s="24"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
+      <c r="L21" s="24">
+        <v>0</v>
+      </c>
+      <c r="M21" s="30">
+        <v>0</v>
+      </c>
+      <c r="N21" s="24">
+        <v>0</v>
+      </c>
+      <c r="O21" s="24">
+        <v>0</v>
+      </c>
+      <c r="P21" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="24">
+        <v>0</v>
+      </c>
+      <c r="R21" s="24">
+        <v>0</v>
+      </c>
       <c r="S21" s="24"/>
     </row>
     <row r="22" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5515,13 +5552,27 @@
       <c r="K22" s="25">
         <v>0</v>
       </c>
-      <c r="L22" s="25"/>
-      <c r="M22" s="56"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
+      <c r="L22" s="25">
+        <v>0</v>
+      </c>
+      <c r="M22" s="56">
+        <v>0</v>
+      </c>
+      <c r="N22" s="25">
+        <v>0</v>
+      </c>
+      <c r="O22" s="25">
+        <v>0</v>
+      </c>
+      <c r="P22" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="25">
+        <v>0</v>
+      </c>
+      <c r="R22" s="25">
+        <v>0</v>
+      </c>
       <c r="S22" s="25"/>
     </row>
     <row r="23" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5540,19 +5591,45 @@
       <c r="E23" s="65">
         <v>1</v>
       </c>
-      <c r="F23" s="56"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="56"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
+      <c r="F23" s="56">
+        <v>1</v>
+      </c>
+      <c r="G23" s="25">
+        <v>1</v>
+      </c>
+      <c r="H23" s="25">
+        <v>1</v>
+      </c>
+      <c r="I23" s="25">
+        <v>1</v>
+      </c>
+      <c r="J23" s="25">
+        <v>1</v>
+      </c>
+      <c r="K23" s="25">
+        <v>1</v>
+      </c>
+      <c r="L23" s="25">
+        <v>1</v>
+      </c>
+      <c r="M23" s="56">
+        <v>1</v>
+      </c>
+      <c r="N23" s="25">
+        <v>1</v>
+      </c>
+      <c r="O23" s="25">
+        <v>1</v>
+      </c>
+      <c r="P23" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="25">
+        <v>1</v>
+      </c>
+      <c r="R23" s="25">
+        <v>2</v>
+      </c>
       <c r="S23" s="25"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
@@ -5565,55 +5642,55 @@
       </c>
       <c r="F24" s="9">
         <f>IF(SUM(F11:F23)&gt;0,E24-SUM(F11:F23),NA())</f>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G24" s="9">
         <f>IF(SUM(G11:G23)&gt;0,E24-SUM(F11:G23),NA())</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H24" s="9">
         <f>IF(SUM(H11:H23)&gt;0,F24-SUM(G11:H23),NA())</f>
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I24" s="9">
         <f>IF(SUM(I11:I23)&gt;0,E24-SUM(F11:I23),NA())</f>
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J24" s="9">
         <f>IF(SUM(J11:J23)&gt;0,E24-SUM(F11:J23),NA())</f>
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="K24" s="9">
         <f>IF(SUM(K11:K23)&gt;0,E24-SUM(F11:K23),NA())</f>
-        <v>6</v>
-      </c>
-      <c r="L24" s="9" t="e">
+        <v>-6</v>
+      </c>
+      <c r="L24" s="9">
         <f>IF(SUM(L11:L23)&gt;0,E24-SUM(F11:L23),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="M24" s="9" t="e">
+        <v>-10</v>
+      </c>
+      <c r="M24" s="9">
         <f>IF(SUM(M11:M23)&gt;0,E24-SUM(F11:M23),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="N24" s="9" t="e">
+        <v>-12</v>
+      </c>
+      <c r="N24" s="9">
         <f>IF(SUM(N11:N23)&gt;0,E24-SUM(F11:N23),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="O24" s="9" t="e">
+        <v>-16</v>
+      </c>
+      <c r="O24" s="9">
         <f>IF(SUM(O11:O23)&gt;0,E24-SUM(F11:O23),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="P24" s="9" t="e">
+        <v>-20</v>
+      </c>
+      <c r="P24" s="9">
         <f>IF(SUM(P11:P23)&gt;0,E24-SUM(F11:P23),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q24" s="9" t="e">
+        <v>-23</v>
+      </c>
+      <c r="Q24" s="9">
         <f>IF(SUM(Q11:Q23)&gt;0,E24-SUM(F11:Q23),NA())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="R24" s="9" t="e">
+        <v>-26</v>
+      </c>
+      <c r="R24" s="9">
         <f>IF(SUM(R11:R23)&gt;0,E24-SUM(F11:R23),NA())</f>
-        <v>#N/A</v>
+        <v>-32</v>
       </c>
       <c r="S24" s="9" t="e">
         <f>IF(SUM(S11:S23)&gt;0,E24-SUM(F11:S23),NA())</f>
@@ -6127,49 +6204,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="31" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="64">
-        <v>2</v>
-      </c>
-      <c r="F11" s="30">
-        <v>0</v>
-      </c>
-      <c r="G11" s="30">
-        <v>0</v>
-      </c>
-      <c r="H11" s="30">
-        <v>1</v>
-      </c>
-      <c r="I11" s="30">
-        <v>0</v>
-      </c>
-      <c r="J11" s="28">
-        <v>1</v>
-      </c>
-      <c r="K11" s="28">
-        <v>1</v>
-      </c>
-      <c r="L11" s="28">
-        <v>0</v>
-      </c>
-      <c r="M11" s="30">
-        <v>0</v>
-      </c>
-      <c r="N11" s="30">
-        <v>1</v>
-      </c>
+    <row r="11" spans="1:19" s="31" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
       <c r="O11" s="30"/>
       <c r="P11" s="30"/>
       <c r="Q11" s="28"/>
@@ -6177,48 +6226,20 @@
       <c r="S11" s="28"/>
     </row>
     <row r="12" spans="1:19" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="64">
-        <v>2</v>
-      </c>
-      <c r="F12" s="30">
-        <v>0</v>
-      </c>
-      <c r="G12" s="30">
-        <v>0</v>
-      </c>
-      <c r="H12" s="30">
-        <v>1</v>
-      </c>
-      <c r="I12" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="J12" s="28">
-        <v>1</v>
-      </c>
-      <c r="K12" s="28">
-        <v>0</v>
-      </c>
-      <c r="L12" s="28">
-        <v>0</v>
-      </c>
-      <c r="M12" s="30">
-        <v>2</v>
-      </c>
-      <c r="N12" s="30">
-        <v>1</v>
-      </c>
+      <c r="A12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
       <c r="O12" s="30"/>
       <c r="P12" s="30"/>
       <c r="Q12" s="28"/>
@@ -6226,48 +6247,20 @@
       <c r="S12" s="28"/>
     </row>
     <row r="13" spans="1:19" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="64">
-        <v>2</v>
-      </c>
-      <c r="F13" s="30">
-        <v>0</v>
-      </c>
-      <c r="G13" s="28">
-        <v>0</v>
-      </c>
-      <c r="H13" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="I13" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="J13" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="K13" s="28">
-        <v>0</v>
-      </c>
-      <c r="L13" s="28">
-        <v>0</v>
-      </c>
-      <c r="M13" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="N13" s="28">
-        <v>0.5</v>
-      </c>
+      <c r="A13" s="27"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="28"/>
       <c r="O13" s="28"/>
       <c r="P13" s="28"/>
       <c r="Q13" s="28"/>
@@ -6275,48 +6268,20 @@
       <c r="S13" s="28"/>
     </row>
     <row r="14" spans="1:19" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="64">
-        <v>2</v>
-      </c>
-      <c r="F14" s="30">
-        <v>0</v>
-      </c>
-      <c r="G14" s="28">
-        <v>0</v>
-      </c>
-      <c r="H14" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="I14" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="J14" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="K14" s="28">
-        <v>0</v>
-      </c>
-      <c r="L14" s="28">
-        <v>0</v>
-      </c>
-      <c r="M14" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="N14" s="28">
-        <v>0.5</v>
-      </c>
+      <c r="A14" s="27"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="28"/>
       <c r="O14" s="28"/>
       <c r="P14" s="28"/>
       <c r="Q14" s="28"/>
@@ -6324,48 +6289,20 @@
       <c r="S14" s="28"/>
     </row>
     <row r="15" spans="1:19" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="64">
-        <v>2</v>
-      </c>
-      <c r="F15" s="30">
-        <v>0</v>
-      </c>
-      <c r="G15" s="28">
-        <v>0</v>
-      </c>
-      <c r="H15" s="28">
-        <v>0</v>
-      </c>
-      <c r="I15" s="28">
-        <v>0</v>
-      </c>
-      <c r="J15" s="28">
-        <v>0</v>
-      </c>
-      <c r="K15" s="28">
-        <v>0</v>
-      </c>
-      <c r="L15" s="28">
-        <v>0</v>
-      </c>
-      <c r="M15" s="30">
-        <v>0</v>
-      </c>
-      <c r="N15" s="28">
-        <v>0</v>
-      </c>
+      <c r="A15" s="27"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="28"/>
       <c r="O15" s="28"/>
       <c r="P15" s="28"/>
       <c r="Q15" s="28"/>
@@ -6373,48 +6310,20 @@
       <c r="S15" s="28"/>
     </row>
     <row r="16" spans="1:19" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="64">
-        <v>3</v>
-      </c>
-      <c r="F16" s="30">
-        <v>0</v>
-      </c>
-      <c r="G16" s="28">
-        <v>0</v>
-      </c>
-      <c r="H16" s="28">
-        <v>0</v>
-      </c>
-      <c r="I16" s="28">
-        <v>0</v>
-      </c>
-      <c r="J16" s="28">
-        <v>0</v>
-      </c>
-      <c r="K16" s="28">
-        <v>0</v>
-      </c>
-      <c r="L16" s="28">
-        <v>0</v>
-      </c>
-      <c r="M16" s="30">
-        <v>0</v>
-      </c>
-      <c r="N16" s="28">
-        <v>0</v>
-      </c>
+      <c r="A16" s="27"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="28"/>
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
@@ -6422,48 +6331,20 @@
       <c r="S16" s="28"/>
     </row>
     <row r="17" spans="1:19" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="61" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="64">
-        <v>2</v>
-      </c>
-      <c r="F17" s="30">
-        <v>0</v>
-      </c>
-      <c r="G17" s="24">
-        <v>0</v>
-      </c>
-      <c r="H17" s="24">
-        <v>0</v>
-      </c>
-      <c r="I17" s="24">
-        <v>0</v>
-      </c>
-      <c r="J17" s="24">
-        <v>0</v>
-      </c>
-      <c r="K17" s="24">
-        <v>0</v>
-      </c>
-      <c r="L17" s="24">
-        <v>0</v>
-      </c>
-      <c r="M17" s="30">
-        <v>0</v>
-      </c>
-      <c r="N17" s="24">
-        <v>0</v>
-      </c>
+      <c r="A17" s="27"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="24"/>
       <c r="O17" s="24"/>
       <c r="P17" s="24"/>
       <c r="Q17" s="24"/>
@@ -6471,48 +6352,20 @@
       <c r="S17" s="24"/>
     </row>
     <row r="18" spans="1:19" s="8" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="62" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="65">
-        <v>1</v>
-      </c>
-      <c r="F18" s="56">
-        <v>0</v>
-      </c>
-      <c r="G18" s="25">
-        <v>0</v>
-      </c>
-      <c r="H18" s="25">
-        <v>1</v>
-      </c>
-      <c r="I18" s="25">
-        <v>0</v>
-      </c>
-      <c r="J18" s="25">
-        <v>1</v>
-      </c>
-      <c r="K18" s="25">
-        <v>0</v>
-      </c>
-      <c r="L18" s="25">
-        <v>0</v>
-      </c>
-      <c r="M18" s="56">
-        <v>0</v>
-      </c>
-      <c r="N18" s="25">
-        <v>2</v>
-      </c>
+      <c r="A18" s="56"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="25"/>
       <c r="O18" s="25"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
@@ -6520,48 +6373,13 @@
       <c r="S18" s="25"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" s="4">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4">
-        <v>0</v>
-      </c>
-      <c r="M19" s="4">
-        <v>0</v>
-      </c>
-      <c r="N19" s="4">
-        <v>0</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
@@ -6569,48 +6387,13 @@
       <c r="S19" s="4"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20" s="4">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4">
-        <v>1</v>
-      </c>
-      <c r="I20" s="4">
-        <v>1</v>
-      </c>
-      <c r="J20" s="4">
-        <v>1</v>
-      </c>
-      <c r="K20" s="4">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4">
-        <v>0</v>
-      </c>
-      <c r="M20" s="4">
-        <v>1</v>
-      </c>
-      <c r="N20" s="4">
-        <v>1</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
@@ -6673,15 +6456,15 @@
       </c>
       <c r="I24" s="9" t="e">
         <f>IF(SUM(I11:I23)&gt;0,E24-SUM(F11:I23),NA())</f>
-        <v>#VALUE!</v>
+        <v>#N/A</v>
       </c>
       <c r="J24" s="9" t="e">
         <f>IF(SUM(J11:J23)&gt;0,E24-SUM(F11:J23),NA())</f>
-        <v>#VALUE!</v>
+        <v>#N/A</v>
       </c>
       <c r="K24" s="9" t="e">
         <f>IF(SUM(K11:K23)&gt;0,E24-SUM(F11:K23),NA())</f>
-        <v>#VALUE!</v>
+        <v>#N/A</v>
       </c>
       <c r="L24" s="9" t="e">
         <f>IF(SUM(L11:L23)&gt;0,E24-SUM(F11:L23),NA())</f>
@@ -6689,11 +6472,11 @@
       </c>
       <c r="M24" s="9" t="e">
         <f>IF(SUM(M11:M23)&gt;0,E24-SUM(F11:M23),NA())</f>
-        <v>#VALUE!</v>
+        <v>#N/A</v>
       </c>
       <c r="N24" s="9" t="e">
         <f>IF(SUM(N11:N23)&gt;0,E24-SUM(F11:N23),NA())</f>
-        <v>#VALUE!</v>
+        <v>#N/A</v>
       </c>
       <c r="O24" s="9" t="e">
         <f>IF(SUM(O11:O23)&gt;0,E24-SUM(F11:O23),NA())</f>
@@ -6821,7 +6604,7 @@
       </c>
       <c r="L30" s="4">
         <f>SUM(E11:E19)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>

--- a/docs/AetherFlow_Sprint1_Updated_v3.xlsx
+++ b/docs/AetherFlow_Sprint1_Updated_v3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la\Documents\Team Project 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\Documents\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7457F3E3-2CA6-4955-B622-55EFDB44FC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D10A288F-8B6D-45F6-B129-7EEDCA7E238C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -5072,13 +5072,27 @@
       <c r="K12" s="28">
         <v>1</v>
       </c>
-      <c r="L12" s="28"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
+      <c r="L12" s="28">
+        <v>0</v>
+      </c>
+      <c r="M12" s="30">
+        <v>1</v>
+      </c>
+      <c r="N12" s="30">
+        <v>2</v>
+      </c>
+      <c r="O12" s="30">
+        <v>1</v>
+      </c>
+      <c r="P12" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="28">
+        <v>1</v>
+      </c>
+      <c r="R12" s="28">
+        <v>2</v>
+      </c>
       <c r="S12" s="28"/>
     </row>
     <row r="13" spans="1:19" s="31" customFormat="1" x14ac:dyDescent="0.2">
@@ -5150,13 +5164,27 @@
       <c r="K14" s="28">
         <v>1</v>
       </c>
-      <c r="L14" s="28"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="28"/>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="28"/>
+      <c r="L14" s="28">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30">
+        <v>1</v>
+      </c>
+      <c r="N14" s="28">
+        <v>1</v>
+      </c>
+      <c r="O14" s="28">
+        <v>1</v>
+      </c>
+      <c r="P14" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="28">
+        <v>1</v>
+      </c>
+      <c r="R14" s="28">
+        <v>1</v>
+      </c>
       <c r="S14" s="28"/>
     </row>
     <row r="15" spans="1:19" s="31" customFormat="1" x14ac:dyDescent="0.2">
@@ -5281,13 +5309,27 @@
       <c r="K17" s="24">
         <v>1</v>
       </c>
-      <c r="L17" s="24"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
+      <c r="L17" s="24">
+        <v>0</v>
+      </c>
+      <c r="M17" s="30">
+        <v>1</v>
+      </c>
+      <c r="N17" s="24">
+        <v>1</v>
+      </c>
+      <c r="O17" s="24">
+        <v>2</v>
+      </c>
+      <c r="P17" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="24">
+        <v>1</v>
+      </c>
+      <c r="R17" s="24">
+        <v>1</v>
+      </c>
       <c r="S17" s="24"/>
     </row>
     <row r="18" spans="1:19" s="8" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5670,27 +5712,27 @@
       </c>
       <c r="M24" s="9">
         <f>IF(SUM(M11:M23)&gt;0,E24-SUM(F11:M23),NA())</f>
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="N24" s="9">
         <f>IF(SUM(N11:N23)&gt;0,E24-SUM(F11:N23),NA())</f>
-        <v>-16</v>
+        <v>-23</v>
       </c>
       <c r="O24" s="9">
         <f>IF(SUM(O11:O23)&gt;0,E24-SUM(F11:O23),NA())</f>
-        <v>-20</v>
+        <v>-31</v>
       </c>
       <c r="P24" s="9">
         <f>IF(SUM(P11:P23)&gt;0,E24-SUM(F11:P23),NA())</f>
-        <v>-23</v>
+        <v>-36</v>
       </c>
       <c r="Q24" s="9">
         <f>IF(SUM(Q11:Q23)&gt;0,E24-SUM(F11:Q23),NA())</f>
-        <v>-26</v>
+        <v>-42</v>
       </c>
       <c r="R24" s="9">
         <f>IF(SUM(R11:R23)&gt;0,E24-SUM(F11:R23),NA())</f>
-        <v>-32</v>
+        <v>-52</v>
       </c>
       <c r="S24" s="9" t="e">
         <f>IF(SUM(S11:S23)&gt;0,E24-SUM(F11:S23),NA())</f>
